--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeReportTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeReportTemplate.xlsx
@@ -4,22 +4,34 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23775" windowHeight="12375" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="23775" windowHeight="12375" firstSheet="5" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="汇总" sheetId="10" r:id="rId1"/>
     <sheet name="1.费用报销单" sheetId="1" r:id="rId2"/>
     <sheet name="2.差旅费用报销单" sheetId="2" r:id="rId3"/>
     <sheet name="3.借支单" sheetId="3" r:id="rId4"/>
-    <sheet name="4.手机截图插入模板（付款截图、签到截图）" sheetId="7" r:id="rId5"/>
-    <sheet name="5.发票截图插入（大截图插入模板）" sheetId="8" r:id="rId6"/>
+    <sheet name="4.手机截图插入模板（付款截图、签到截图） (3)" sheetId="13" r:id="rId5"/>
+    <sheet name="5.发票截图插入（大截图插入模板） (4)" sheetId="16" r:id="rId6"/>
+    <sheet name="4.手机截图插入模板（付款截图、签到截图） (4)" sheetId="15" r:id="rId7"/>
+    <sheet name="4.手机截图插入模板（付款截图、签到截图）" sheetId="7" r:id="rId8"/>
+    <sheet name="5.发票截图插入（大截图插入模板）" sheetId="8" r:id="rId9"/>
+    <sheet name="5.发票截图插入（大截图插入模板） (3)" sheetId="14" r:id="rId10"/>
+    <sheet name="4.手机截图插入模板（付款截图、签到截图） (2)" sheetId="11" r:id="rId11"/>
+    <sheet name="5.发票截图插入（大截图插入模板） (2)" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'1.费用报销单'!$A$1:$F$15</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'2.差旅费用报销单'!$A$1:$L$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'3.借支单'!$A$1:$H$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'4.手机截图插入模板（付款截图、签到截图）'!$A$1:$I$53</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'5.发票截图插入（大截图插入模板）'!$A$1:$I$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'4.手机截图插入模板（付款截图、签到截图）'!$A$1:$C$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'5.发票截图插入（大截图插入模板）'!$A$1:$A$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'4.手机截图插入模板（付款截图、签到截图） (2)'!$A$1:$I$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'5.发票截图插入（大截图插入模板） (2)'!$A$1:$I$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'4.手机截图插入模板（付款截图、签到截图） (3)'!$A$1:$C$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'5.发票截图插入（大截图插入模板） (3)'!$A$1:$A$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'4.手机截图插入模板（付款截图、签到截图） (4)'!$A$1:$C$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'5.发票截图插入（大截图插入模板） (4)'!$A$1:$A$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -115,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="153">
   <si>
     <t>费用报销单据模版 汇总表</t>
   </si>
@@ -714,28 +726,40 @@
     <t>财务主管：</t>
   </si>
   <si>
+    <t>{data.image1}</t>
+  </si>
+  <si>
+    <t>{data.image2}</t>
+  </si>
+  <si>
+    <t>3说明：</t>
+  </si>
+  <si>
+    <t>4说明：</t>
+  </si>
+  <si>
+    <t>图3</t>
+  </si>
+  <si>
+    <t>图四</t>
+  </si>
+  <si>
+    <t>1说明：几月几日在那陪同谁吃饭</t>
+  </si>
+  <si>
+    <t>不可改动表格格式，只需插入图片和修改说明即可，注意：插入图片方式为嵌入表格式</t>
+  </si>
+  <si>
+    <t>2说明：</t>
+  </si>
+  <si>
     <t>{memo1}</t>
   </si>
   <si>
     <t>2说明：同理</t>
   </si>
   <si>
-    <t>不可改动表格格式，只需插入图片和修改说明即可，注意：插入图片方式为嵌入表格式</t>
-  </si>
-  <si>
     <t>{}</t>
-  </si>
-  <si>
-    <t>3说明：</t>
-  </si>
-  <si>
-    <t>4说明：</t>
-  </si>
-  <si>
-    <t>1说明：几月几日在那陪同谁吃饭</t>
-  </si>
-  <si>
-    <t>2说明：</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1272,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -1356,6 +1380,21 @@
       </right>
       <top/>
       <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashDot">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="dashDot">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="dashed">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="dashed">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -1757,7 +1796,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="32" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="33" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1769,34 +1808,34 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="37" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="37" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1881,7 +1920,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1966,6 +2005,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1984,33 +2039,33 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2031,7 +2086,7 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2043,7 +2098,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2051,23 +2106,23 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2075,10 +2130,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="177" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2087,11 +2138,15 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2127,7 +2182,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2135,10 +2190,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2147,11 +2198,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2159,7 +2214,7 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2167,7 +2222,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2189,11 +2244,11 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="7" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="7" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="7" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="7" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2209,11 +2264,11 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2221,11 +2276,11 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2251,7 +2306,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2279,7 +2334,7 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2297,55 +2352,55 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2534,7 +2589,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2" descr="Screenshot_2024-06-21-10-55-25-069_com.tencent.mm"/>
+        <xdr:cNvPr id="2" name="图片 1" descr="Screenshot_2024-06-21-10-55-25-069_com.tencent.mm"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2572,7 +2627,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="图片 5" descr="Screenshot_2024-06-21-10-55-37-436_com.tencent.mm"/>
+        <xdr:cNvPr id="3" name="图片 2" descr="Screenshot_2024-06-21-10-55-37-436_com.tencent.mm"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2940,119 +2995,119 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="34.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15" style="109" customWidth="1"/>
-    <col min="2" max="2" width="28.625" style="109" customWidth="1"/>
-    <col min="3" max="3" width="40.25" style="109" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="109"/>
+    <col min="1" max="1" width="15" style="113" customWidth="1"/>
+    <col min="2" max="2" width="28.625" style="113" customWidth="1"/>
+    <col min="3" max="3" width="40.25" style="113" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="113"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:3">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="112"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="116"/>
     </row>
     <row r="2" ht="20.25" customHeight="1" spans="1:3">
-      <c r="A2" s="113"/>
-      <c r="B2" s="113"/>
-      <c r="C2" s="113"/>
-    </row>
-    <row r="3" s="108" customFormat="1" customHeight="1" spans="1:3">
-      <c r="A3" s="114" t="s">
+      <c r="A2" s="117"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+    </row>
+    <row r="3" s="112" customFormat="1" customHeight="1" spans="1:3">
+      <c r="A3" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="115" t="s">
+      <c r="B3" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="116" t="s">
+      <c r="C3" s="120" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" s="108" customFormat="1" customHeight="1" spans="1:3">
-      <c r="A4" s="117">
+    <row r="4" s="112" customFormat="1" customHeight="1" spans="1:3">
+      <c r="A4" s="121">
         <v>1</v>
       </c>
-      <c r="B4" s="118" t="s">
+      <c r="B4" s="122" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="123" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" s="108" customFormat="1" customHeight="1" spans="1:3">
-      <c r="A5" s="120">
+    <row r="5" s="112" customFormat="1" customHeight="1" spans="1:3">
+      <c r="A5" s="124">
         <v>2</v>
       </c>
-      <c r="B5" s="121" t="s">
+      <c r="B5" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="122" t="s">
+      <c r="C5" s="126" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" s="108" customFormat="1" customHeight="1" spans="1:3">
-      <c r="A6" s="120">
+    <row r="6" s="112" customFormat="1" customHeight="1" spans="1:3">
+      <c r="A6" s="124">
         <v>3</v>
       </c>
-      <c r="B6" s="121" t="s">
+      <c r="B6" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="122" t="s">
+      <c r="C6" s="126" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" s="108" customFormat="1" hidden="1" customHeight="1" spans="1:9">
-      <c r="A7" s="120">
+    <row r="7" s="112" customFormat="1" hidden="1" customHeight="1" spans="1:9">
+      <c r="A7" s="124">
         <v>4</v>
       </c>
-      <c r="B7" s="121" t="s">
+      <c r="B7" s="125" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="122" t="s">
+      <c r="C7" s="126" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="108">
+      <c r="G7" s="112">
         <v>1</v>
       </c>
-      <c r="H7" s="108">
+      <c r="H7" s="112">
         <v>1</v>
       </c>
-      <c r="I7" s="108">
+      <c r="I7" s="112">
         <f>G7+H7</f>
         <v>2</v>
       </c>
     </row>
-    <row r="8" s="108" customFormat="1" hidden="1" customHeight="1" spans="1:3">
-      <c r="A8" s="120">
+    <row r="8" s="112" customFormat="1" hidden="1" customHeight="1" spans="1:3">
+      <c r="A8" s="124">
         <v>5</v>
       </c>
-      <c r="B8" s="123" t="s">
+      <c r="B8" s="127" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="122" t="s">
+      <c r="C8" s="126" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" s="108" customFormat="1" customHeight="1" spans="1:3">
-      <c r="A9" s="120">
+    <row r="9" s="112" customFormat="1" customHeight="1" spans="1:3">
+      <c r="A9" s="124">
         <v>4</v>
       </c>
-      <c r="B9" s="121" t="s">
+      <c r="B9" s="125" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="122" t="s">
+      <c r="C9" s="126" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" s="108" customFormat="1" customHeight="1" spans="1:3">
-      <c r="A10" s="124">
+    <row r="10" s="112" customFormat="1" customHeight="1" spans="1:3">
+      <c r="A10" s="128">
         <v>5</v>
       </c>
-      <c r="B10" s="125" t="s">
+      <c r="B10" s="129" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="126" t="s">
+      <c r="C10" s="130" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3062,6 +3117,1439 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="5"/>
+  <cols>
+    <col min="1" max="1" width="76.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.1" customHeight="1" spans="1:13">
+      <c r="A1" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+    </row>
+    <row r="2" ht="329" customHeight="1" spans="1:13">
+      <c r="A2" s="13"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="1:1">
+      <c r="A3" s="9"/>
+    </row>
+    <row r="4" ht="30.95" customHeight="1" spans="1:1">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="1:1">
+      <c r="A5" s="11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" ht="329" customHeight="1" spans="1:1">
+      <c r="A6" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D1:I2"/>
+    <mergeCell ref="J1:M2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:T53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
+  <cols>
+    <col min="4" max="4" width="5.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="4.875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.1" customHeight="1" spans="1:20">
+      <c r="A1" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="K1" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:20">
+      <c r="A2" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="15"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:20">
+      <c r="A3" s="5"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="16"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:20">
+      <c r="A4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="16"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+    </row>
+    <row r="5" ht="14.25" customHeight="1" spans="1:20">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="16"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:9">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="16"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:9">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="16"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:9">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="16"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:12">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="16"/>
+      <c r="L9" s="21"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:9">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="16"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:9">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="16"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:9">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="16"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:9">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="16"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:9">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="16"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:9">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="16"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:9">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="16"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:9">
+      <c r="A17" s="5"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="16"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:9">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="16"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:9">
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="16"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:9">
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="16"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:9">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="16"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:9">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="16"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:9">
+      <c r="A23" s="5"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="16"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:9">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="16"/>
+    </row>
+    <row r="25" ht="59.1" customHeight="1" spans="1:9">
+      <c r="A25" s="7"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="17"/>
+    </row>
+    <row r="26" ht="36" customHeight="1" spans="1:9">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+    </row>
+    <row r="27" ht="30.95" customHeight="1" spans="1:9">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+    </row>
+    <row r="28" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A28" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:9">
+      <c r="A29" s="3"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="15"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:9">
+      <c r="A30" s="5"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="16"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:9">
+      <c r="A31" s="5"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="16"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:9">
+      <c r="A32" s="5"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="16"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:9">
+      <c r="A33" s="5"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="16"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:9">
+      <c r="A34" s="5"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="16"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:9">
+      <c r="A35" s="5"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="16"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:9">
+      <c r="A36" s="5"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="16"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:9">
+      <c r="A37" s="5"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="16"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:9">
+      <c r="A38" s="5"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="16"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:9">
+      <c r="A39" s="5"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="16"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:9">
+      <c r="A40" s="5"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="16"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:9">
+      <c r="A41" s="5"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="16"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:9">
+      <c r="A42" s="5"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="16"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:9">
+      <c r="A43" s="5"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="16"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:9">
+      <c r="A44" s="5"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="16"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:9">
+      <c r="A45" s="5"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="16"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:9">
+      <c r="A46" s="5"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="16"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:9">
+      <c r="A47" s="5"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="16"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:9">
+      <c r="A48" s="5"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="16"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:9">
+      <c r="A49" s="5"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="16"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:9">
+      <c r="A50" s="5"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="16"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:9">
+      <c r="A51" s="5"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="16"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:9">
+      <c r="A52" s="5"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="16"/>
+    </row>
+    <row r="53" ht="42" customHeight="1" spans="1:9">
+      <c r="A53" s="7"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="17"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange sqref="F29" name="区域4"/>
+    <protectedRange sqref="A2" name="区域1"/>
+    <protectedRange sqref="F2" name="区域2"/>
+    <protectedRange sqref="A29" name="区域3"/>
+  </protectedRanges>
+  <mergeCells count="12">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="K5:P5"/>
+    <mergeCell ref="Q5:T5"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="K1:P4"/>
+    <mergeCell ref="Q1:T4"/>
+    <mergeCell ref="A2:D25"/>
+    <mergeCell ref="F2:I25"/>
+    <mergeCell ref="A29:D53"/>
+    <mergeCell ref="F29:I53"/>
+  </mergeCells>
+  <pageMargins left="1.02361111111111" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:U53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
+  <cols>
+    <col min="4" max="4" width="11.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="1" customWidth="1"/>
+    <col min="8" max="8" width="4.25" customWidth="1"/>
+    <col min="9" max="9" width="7.375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.1" customHeight="1" spans="1:21">
+      <c r="A1" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="L1" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:21">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="15"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:21">
+      <c r="A3" s="5"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="16"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:21">
+      <c r="A4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="16"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+    </row>
+    <row r="5" ht="14.25" customHeight="1" spans="1:21">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="16"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:9">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="16"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:9">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="16"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:9">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="16"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:9">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="16"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:9">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="16"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:9">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="16"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:9">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="16"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:9">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="16"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:9">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="16"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:9">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="16"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:9">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="16"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:9">
+      <c r="A17" s="5"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="16"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:9">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="16"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:9">
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="16"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:9">
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="16"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:9">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="16"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:9">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="16"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:9">
+      <c r="A23" s="5"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="16"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:9">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="16"/>
+    </row>
+    <row r="25" ht="17.1" customHeight="1" spans="1:9">
+      <c r="A25" s="7"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="17"/>
+    </row>
+    <row r="26" ht="36" customHeight="1" spans="1:9">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+    </row>
+    <row r="27" ht="30.95" customHeight="1" spans="1:9">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+    </row>
+    <row r="28" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A28" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:9">
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:9">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:9">
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:9">
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:9">
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:9">
+      <c r="A34" s="13"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:9">
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:9">
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:9">
+      <c r="A37" s="13"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:9">
+      <c r="A38" s="13"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:9">
+      <c r="A39" s="13"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:9">
+      <c r="A40" s="13"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:9">
+      <c r="A41" s="13"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:9">
+      <c r="A42" s="13"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:9">
+      <c r="A43" s="13"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:9">
+      <c r="A44" s="13"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:9">
+      <c r="A45" s="13"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:9">
+      <c r="A46" s="13"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:9">
+      <c r="A47" s="13"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:9">
+      <c r="A48" s="13"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:9">
+      <c r="A49" s="13"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:9">
+      <c r="A50" s="13"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:9">
+      <c r="A51" s="13"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:9">
+      <c r="A52" s="13"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+    </row>
+    <row r="53" customHeight="1" spans="1:9">
+      <c r="A53" s="13"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="13"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange sqref="F2" name="区域2"/>
+    <protectedRange sqref="A2" name="区域1"/>
+    <protectedRange sqref="F29" name="区域4"/>
+    <protectedRange sqref="A29" name="区域3"/>
+  </protectedRanges>
+  <mergeCells count="8">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="L5:Q5"/>
+    <mergeCell ref="R5:U5"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="L1:Q4"/>
+    <mergeCell ref="R1:U4"/>
+    <mergeCell ref="A2:I25"/>
+    <mergeCell ref="A29:I53"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3081,516 +4569,516 @@
     <col min="5" max="5" width="19.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="18.625" style="1" customWidth="1"/>
     <col min="9" max="9" width="36.375" style="21" customWidth="1"/>
-    <col min="10" max="17" width="9" style="94"/>
+    <col min="10" max="17" width="9" style="98"/>
   </cols>
   <sheetData>
     <row r="1" ht="84" customHeight="1" spans="1:6">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
     </row>
     <row r="2" ht="35.1" customHeight="1" spans="1:17">
-      <c r="A2" s="95" t="s">
+      <c r="A2" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="100" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="97" t="s">
+      <c r="C2" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="97"/>
-      <c r="E2" s="98" t="s">
+      <c r="D2" s="101"/>
+      <c r="E2" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="37"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="78"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="82"/>
+      <c r="Q2" s="82"/>
     </row>
     <row r="3" ht="35.1" customHeight="1" spans="1:17">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="45" t="s">
+      <c r="C3" s="51"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="F3" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="37"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="78"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:17">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="99" t="s">
+      <c r="B4" s="103" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="67" t="s">
+      <c r="C4" s="103"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="67" t="s">
+      <c r="F4" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="37"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="78"/>
-      <c r="K4" s="78"/>
-      <c r="L4" s="78"/>
-      <c r="M4" s="78"/>
-      <c r="N4" s="78"/>
-      <c r="O4" s="78"/>
-      <c r="P4" s="78"/>
-      <c r="Q4" s="78"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="82"/>
+      <c r="O4" s="82"/>
+      <c r="P4" s="82"/>
+      <c r="Q4" s="82"/>
     </row>
     <row r="5" ht="45" customHeight="1" spans="1:17">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="94" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="103" t="s">
+      <c r="C5" s="106"/>
+      <c r="D5" s="107" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="82" t="s">
+      <c r="E5" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="83"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="78"/>
-      <c r="K5" s="78"/>
-      <c r="L5" s="78"/>
-      <c r="M5" s="78"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
+      <c r="F5" s="87"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
+      <c r="L5" s="82"/>
+      <c r="M5" s="82"/>
+      <c r="N5" s="82"/>
+      <c r="O5" s="82"/>
+      <c r="P5" s="82"/>
+      <c r="Q5" s="82"/>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:17">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="84" t="s">
+      <c r="E6" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="49" t="s">
+      <c r="F6" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="37"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="78"/>
-      <c r="L6" s="78"/>
-      <c r="M6" s="78"/>
-      <c r="N6" s="78"/>
-      <c r="O6" s="78"/>
-      <c r="P6" s="78"/>
-      <c r="Q6" s="78"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="82"/>
+      <c r="K6" s="82"/>
+      <c r="L6" s="82"/>
+      <c r="M6" s="82"/>
+      <c r="N6" s="82"/>
+      <c r="O6" s="82"/>
+      <c r="P6" s="82"/>
+      <c r="Q6" s="82"/>
     </row>
     <row r="7" ht="45" customHeight="1" spans="1:17">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="84" t="s">
+      <c r="E7" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="49" t="s">
+      <c r="F7" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="37"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="78"/>
-      <c r="K7" s="78"/>
-      <c r="L7" s="78"/>
-      <c r="M7" s="78"/>
-      <c r="N7" s="78"/>
-      <c r="O7" s="78"/>
-      <c r="P7" s="78"/>
-      <c r="Q7" s="78"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="82"/>
+      <c r="M7" s="82"/>
+      <c r="N7" s="82"/>
+      <c r="O7" s="82"/>
+      <c r="P7" s="82"/>
+      <c r="Q7" s="82"/>
     </row>
     <row r="8" ht="45" customHeight="1" spans="1:17">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="62" t="s">
         <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="85" t="s">
+      <c r="C8" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="85" t="s">
+      <c r="D8" s="89" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="85" t="s">
+      <c r="E8" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="85" t="s">
+      <c r="F8" s="89" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="37"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="78"/>
-      <c r="K8" s="78"/>
-      <c r="L8" s="78"/>
-      <c r="M8" s="78"/>
-      <c r="N8" s="78"/>
-      <c r="O8" s="78"/>
-      <c r="P8" s="78"/>
-      <c r="Q8" s="78"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="82"/>
+      <c r="L8" s="82"/>
+      <c r="M8" s="82"/>
+      <c r="N8" s="82"/>
+      <c r="O8" s="82"/>
+      <c r="P8" s="82"/>
+      <c r="Q8" s="82"/>
     </row>
     <row r="9" ht="45" customHeight="1" spans="1:17">
-      <c r="A9" s="104" t="s">
+      <c r="A9" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="104"/>
-      <c r="C9" s="104"/>
-      <c r="D9" s="104"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="78"/>
-      <c r="K9" s="78"/>
-      <c r="L9" s="78"/>
-      <c r="M9" s="78"/>
-      <c r="N9" s="78"/>
-      <c r="O9" s="78"/>
-      <c r="P9" s="78"/>
-      <c r="Q9" s="78"/>
+      <c r="B9" s="108"/>
+      <c r="C9" s="108"/>
+      <c r="D9" s="108"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="108"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="82"/>
+      <c r="K9" s="82"/>
+      <c r="L9" s="82"/>
+      <c r="M9" s="82"/>
+      <c r="N9" s="82"/>
+      <c r="O9" s="82"/>
+      <c r="P9" s="82"/>
+      <c r="Q9" s="82"/>
     </row>
     <row r="10" ht="45" customHeight="1" spans="1:16">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="78"/>
-      <c r="K10" s="78"/>
-      <c r="L10" s="78"/>
-      <c r="M10" s="78"/>
-      <c r="N10" s="78"/>
-      <c r="O10" s="78"/>
-      <c r="P10" s="78"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="82"/>
+      <c r="K10" s="82"/>
+      <c r="L10" s="82"/>
+      <c r="M10" s="82"/>
+      <c r="N10" s="82"/>
+      <c r="O10" s="82"/>
+      <c r="P10" s="82"/>
     </row>
     <row r="11" ht="35.1" customHeight="1" spans="1:16">
-      <c r="A11" s="95" t="s">
+      <c r="A11" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="96" t="s">
+      <c r="B11" s="100" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="97" t="s">
+      <c r="C11" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="97"/>
-      <c r="E11" s="98" t="s">
+      <c r="D11" s="101"/>
+      <c r="E11" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="37"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="78"/>
-      <c r="K11" s="78"/>
-      <c r="L11" s="78"/>
-      <c r="M11" s="78"/>
-      <c r="N11" s="78"/>
-      <c r="O11" s="78"/>
-      <c r="P11" s="78"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="82"/>
+      <c r="K11" s="82"/>
+      <c r="L11" s="82"/>
+      <c r="M11" s="82"/>
+      <c r="N11" s="82"/>
+      <c r="O11" s="82"/>
+      <c r="P11" s="82"/>
     </row>
     <row r="12" ht="35.1" customHeight="1" spans="1:16">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="45" t="s">
+      <c r="E12" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="45" t="s">
+      <c r="F12" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="37"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="78"/>
-      <c r="N12" s="78"/>
-      <c r="O12" s="78"/>
-      <c r="P12" s="78"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="82"/>
+      <c r="L12" s="82"/>
+      <c r="M12" s="82"/>
+      <c r="N12" s="82"/>
+      <c r="O12" s="82"/>
+      <c r="P12" s="82"/>
     </row>
     <row r="13" ht="35.1" customHeight="1" spans="1:16">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="67" t="s">
+      <c r="B13" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="105" t="s">
+      <c r="C13" s="109" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="67" t="s">
+      <c r="D13" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="E13" s="67" t="s">
+      <c r="E13" s="71" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="67" t="s">
+      <c r="F13" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="H13" s="37"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="78"/>
-      <c r="N13" s="78"/>
-      <c r="O13" s="78"/>
-      <c r="P13" s="78"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="82"/>
+      <c r="K13" s="82"/>
+      <c r="L13" s="82"/>
+      <c r="M13" s="82"/>
+      <c r="N13" s="82"/>
+      <c r="O13" s="82"/>
+      <c r="P13" s="82"/>
     </row>
     <row r="14" ht="35.1" customHeight="1" spans="1:6">
-      <c r="A14" s="52" t="s">
+      <c r="A14" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="106" t="s">
+      <c r="B14" s="110" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="56" t="s">
         <v>66</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="71" t="s">
+      <c r="E14" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="107" t="s">
+      <c r="F14" s="111" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="15" ht="35.1" customHeight="1" spans="1:6">
-      <c r="A15" s="58" t="s">
+      <c r="A15" s="62" t="s">
         <v>47</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="85" t="s">
+      <c r="C15" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="85" t="s">
+      <c r="D15" s="89" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="85" t="s">
+      <c r="E15" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="85" t="s">
+      <c r="F15" s="89" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="16" ht="50.1" customHeight="1"/>
     <row r="17" ht="54.95" customHeight="1" spans="8:17">
-      <c r="H17" s="37"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="78"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="78"/>
-      <c r="M17" s="78"/>
-      <c r="N17" s="78"/>
-      <c r="O17" s="78"/>
-      <c r="P17" s="78"/>
-      <c r="Q17" s="78"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="81"/>
+      <c r="J17" s="82"/>
+      <c r="K17" s="82"/>
+      <c r="L17" s="82"/>
+      <c r="M17" s="82"/>
+      <c r="N17" s="82"/>
+      <c r="O17" s="82"/>
+      <c r="P17" s="82"/>
+      <c r="Q17" s="82"/>
     </row>
     <row r="18" ht="39" customHeight="1" spans="8:17">
-      <c r="H18" s="37"/>
-      <c r="I18" s="77"/>
-      <c r="J18" s="78"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="78"/>
-      <c r="M18" s="78"/>
-      <c r="N18" s="78"/>
-      <c r="O18" s="78"/>
-      <c r="P18" s="78"/>
-      <c r="Q18" s="78"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="82"/>
+      <c r="K18" s="82"/>
+      <c r="L18" s="82"/>
+      <c r="M18" s="82"/>
+      <c r="N18" s="82"/>
+      <c r="O18" s="82"/>
+      <c r="P18" s="82"/>
+      <c r="Q18" s="82"/>
     </row>
     <row r="19" ht="35.1" customHeight="1" spans="8:17">
-      <c r="H19" s="37"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="78"/>
-      <c r="K19" s="78"/>
-      <c r="L19" s="78"/>
-      <c r="M19" s="78"/>
-      <c r="N19" s="78"/>
-      <c r="O19" s="78"/>
-      <c r="P19" s="78"/>
-      <c r="Q19" s="78"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="82"/>
+      <c r="K19" s="82"/>
+      <c r="L19" s="82"/>
+      <c r="M19" s="82"/>
+      <c r="N19" s="82"/>
+      <c r="O19" s="82"/>
+      <c r="P19" s="82"/>
+      <c r="Q19" s="82"/>
     </row>
     <row r="20" ht="45" customHeight="1" spans="8:17">
-      <c r="H20" s="37"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="78"/>
-      <c r="K20" s="78"/>
-      <c r="L20" s="78"/>
-      <c r="M20" s="78"/>
-      <c r="N20" s="78"/>
-      <c r="O20" s="78"/>
-      <c r="P20" s="78"/>
-      <c r="Q20" s="78"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="82"/>
+      <c r="K20" s="82"/>
+      <c r="L20" s="82"/>
+      <c r="M20" s="82"/>
+      <c r="N20" s="82"/>
+      <c r="O20" s="82"/>
+      <c r="P20" s="82"/>
+      <c r="Q20" s="82"/>
     </row>
     <row r="21" ht="45" customHeight="1" spans="8:17">
-      <c r="H21" s="37"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="78"/>
-      <c r="K21" s="78"/>
-      <c r="L21" s="78"/>
-      <c r="M21" s="78"/>
-      <c r="N21" s="78"/>
-      <c r="O21" s="78"/>
-      <c r="P21" s="78"/>
-      <c r="Q21" s="78"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="81"/>
+      <c r="J21" s="82"/>
+      <c r="K21" s="82"/>
+      <c r="L21" s="82"/>
+      <c r="M21" s="82"/>
+      <c r="N21" s="82"/>
+      <c r="O21" s="82"/>
+      <c r="P21" s="82"/>
+      <c r="Q21" s="82"/>
     </row>
     <row r="22" ht="45" customHeight="1" spans="8:17">
-      <c r="H22" s="37"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="78"/>
-      <c r="L22" s="78"/>
-      <c r="M22" s="78"/>
-      <c r="N22" s="78"/>
-      <c r="O22" s="78"/>
-      <c r="P22" s="78"/>
-      <c r="Q22" s="78"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="81"/>
+      <c r="J22" s="82"/>
+      <c r="K22" s="82"/>
+      <c r="L22" s="82"/>
+      <c r="M22" s="82"/>
+      <c r="N22" s="82"/>
+      <c r="O22" s="82"/>
+      <c r="P22" s="82"/>
+      <c r="Q22" s="82"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="8:17">
-      <c r="H23" s="37"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="78"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="78"/>
-      <c r="N23" s="78"/>
-      <c r="O23" s="78"/>
-      <c r="P23" s="78"/>
-      <c r="Q23" s="78"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="82"/>
+      <c r="K23" s="82"/>
+      <c r="L23" s="82"/>
+      <c r="M23" s="82"/>
+      <c r="N23" s="82"/>
+      <c r="O23" s="82"/>
+      <c r="P23" s="82"/>
+      <c r="Q23" s="82"/>
     </row>
     <row r="24" ht="45" hidden="1" customHeight="1" spans="8:17">
-      <c r="H24" s="37"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="78"/>
-      <c r="K24" s="78"/>
-      <c r="L24" s="78"/>
-      <c r="M24" s="78"/>
-      <c r="N24" s="78"/>
-      <c r="O24" s="78"/>
-      <c r="P24" s="78"/>
-      <c r="Q24" s="78"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="81"/>
+      <c r="J24" s="82"/>
+      <c r="K24" s="82"/>
+      <c r="L24" s="82"/>
+      <c r="M24" s="82"/>
+      <c r="N24" s="82"/>
+      <c r="O24" s="82"/>
+      <c r="P24" s="82"/>
+      <c r="Q24" s="82"/>
     </row>
     <row r="25" ht="45" hidden="1" customHeight="1" spans="8:17">
-      <c r="H25" s="37"/>
-      <c r="I25" s="77"/>
-      <c r="J25" s="78"/>
-      <c r="K25" s="78"/>
-      <c r="L25" s="78"/>
-      <c r="M25" s="78"/>
-      <c r="N25" s="78"/>
-      <c r="O25" s="78"/>
-      <c r="P25" s="78"/>
-      <c r="Q25" s="78"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="81"/>
+      <c r="J25" s="82"/>
+      <c r="K25" s="82"/>
+      <c r="L25" s="82"/>
+      <c r="M25" s="82"/>
+      <c r="N25" s="82"/>
+      <c r="O25" s="82"/>
+      <c r="P25" s="82"/>
+      <c r="Q25" s="82"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="8:17">
-      <c r="H26" s="37"/>
-      <c r="I26" s="77"/>
-      <c r="J26" s="78"/>
-      <c r="K26" s="78"/>
-      <c r="L26" s="78"/>
-      <c r="M26" s="78"/>
-      <c r="N26" s="78"/>
-      <c r="O26" s="78"/>
-      <c r="P26" s="78"/>
-      <c r="Q26" s="78"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="81"/>
+      <c r="J26" s="82"/>
+      <c r="K26" s="82"/>
+      <c r="L26" s="82"/>
+      <c r="M26" s="82"/>
+      <c r="N26" s="82"/>
+      <c r="O26" s="82"/>
+      <c r="P26" s="82"/>
+      <c r="Q26" s="82"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="8:17">
-      <c r="H27" s="37"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="78"/>
-      <c r="K27" s="78"/>
-      <c r="L27" s="78"/>
-      <c r="M27" s="78"/>
-      <c r="N27" s="78"/>
-      <c r="O27" s="78"/>
-      <c r="P27" s="78"/>
-      <c r="Q27" s="78"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="82"/>
+      <c r="K27" s="82"/>
+      <c r="L27" s="82"/>
+      <c r="M27" s="82"/>
+      <c r="N27" s="82"/>
+      <c r="O27" s="82"/>
+      <c r="P27" s="82"/>
+      <c r="Q27" s="82"/>
     </row>
     <row r="28" ht="45" customHeight="1"/>
     <row r="29" ht="45" customHeight="1"/>
     <row r="30" ht="35.1" customHeight="1" spans="8:8">
-      <c r="H30" s="37"/>
+      <c r="H30" s="41"/>
     </row>
     <row r="31" ht="29.1" customHeight="1"/>
   </sheetData>
@@ -3661,782 +5149,782 @@
   </cols>
   <sheetData>
     <row r="1" ht="50.1" customHeight="1" spans="1:12">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
     </row>
     <row r="2" ht="35.1" customHeight="1" spans="1:12">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="43" t="s">
+      <c r="E2" s="46"/>
+      <c r="F2" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="28" t="s">
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="74" t="s">
+      <c r="L2" s="78" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" ht="45" customHeight="1" spans="1:23">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44" t="s">
+      <c r="B3" s="48"/>
+      <c r="C3" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46" t="s">
+      <c r="D3" s="49"/>
+      <c r="E3" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="F3" s="46"/>
-      <c r="G3" s="45" t="s">
+      <c r="F3" s="50"/>
+      <c r="G3" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="H3" s="45"/>
-      <c r="I3" s="75" t="s">
+      <c r="H3" s="49"/>
+      <c r="I3" s="79" t="s">
         <v>78</v>
       </c>
-      <c r="J3" s="46"/>
-      <c r="K3" s="76" t="s">
+      <c r="J3" s="50"/>
+      <c r="K3" s="80" t="s">
         <v>79</v>
       </c>
-      <c r="L3" s="76" t="s">
+      <c r="L3" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="37">
+      <c r="N3" s="41">
         <v>1</v>
       </c>
-      <c r="O3" s="77" t="s">
+      <c r="O3" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="P3" s="78" t="s">
+      <c r="P3" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="Q3" s="78"/>
-      <c r="R3" s="78"/>
-      <c r="S3" s="78"/>
-      <c r="T3" s="78"/>
-      <c r="U3" s="78"/>
-      <c r="V3" s="78"/>
-      <c r="W3" s="78"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="82"/>
+      <c r="U3" s="82"/>
+      <c r="V3" s="82"/>
+      <c r="W3" s="82"/>
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:23">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="47" t="s">
+      <c r="E4" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="48" t="s">
+      <c r="F4" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="44" t="s">
+      <c r="G4" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="H4" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="I4" s="44" t="s">
+      <c r="I4" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="J4" s="48" t="s">
+      <c r="J4" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="N4" s="37">
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="N4" s="41">
         <v>2</v>
       </c>
-      <c r="O4" s="77" t="s">
+      <c r="O4" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="P4" s="78" t="s">
+      <c r="P4" s="82" t="s">
         <v>88</v>
       </c>
-      <c r="Q4" s="78"/>
-      <c r="R4" s="78"/>
-      <c r="S4" s="78"/>
-      <c r="T4" s="78"/>
-      <c r="U4" s="78"/>
-      <c r="V4" s="78"/>
-      <c r="W4" s="78"/>
+      <c r="Q4" s="82"/>
+      <c r="R4" s="82"/>
+      <c r="S4" s="82"/>
+      <c r="T4" s="82"/>
+      <c r="U4" s="82"/>
+      <c r="V4" s="82"/>
+      <c r="W4" s="82"/>
     </row>
     <row r="5" ht="45" customHeight="1" spans="1:23">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="49" t="s">
+      <c r="C5" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="D5" s="49" t="s">
+      <c r="D5" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="F5" s="51" t="s">
+      <c r="F5" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="G5" s="49" t="s">
+      <c r="G5" s="53" t="s">
         <v>95</v>
       </c>
-      <c r="H5" s="49" t="s">
+      <c r="H5" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="I5" s="49" t="s">
+      <c r="I5" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="J5" s="49" t="s">
+      <c r="J5" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="K5" s="49" t="s">
+      <c r="K5" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="L5" s="79" t="s">
+      <c r="L5" s="83" t="s">
         <v>100</v>
       </c>
-      <c r="N5" s="37">
+      <c r="N5" s="41">
         <v>3</v>
       </c>
-      <c r="O5" s="77" t="s">
+      <c r="O5" s="81" t="s">
         <v>101</v>
       </c>
-      <c r="P5" s="78" t="s">
+      <c r="P5" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
-      <c r="W5" s="78"/>
+      <c r="Q5" s="82"/>
+      <c r="R5" s="82"/>
+      <c r="S5" s="82"/>
+      <c r="T5" s="82"/>
+      <c r="U5" s="82"/>
+      <c r="V5" s="82"/>
+      <c r="W5" s="82"/>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:23">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="80" t="s">
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="84" t="s">
         <v>104</v>
       </c>
-      <c r="J6" s="81"/>
-      <c r="K6" s="82" t="s">
+      <c r="J6" s="85"/>
+      <c r="K6" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="83"/>
-      <c r="N6" s="37">
+      <c r="L6" s="87"/>
+      <c r="N6" s="41">
         <v>4</v>
       </c>
-      <c r="O6" s="77" t="s">
+      <c r="O6" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="82" t="s">
         <v>105</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78"/>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
-      <c r="V6" s="78"/>
-      <c r="W6" s="78"/>
+      <c r="Q6" s="82"/>
+      <c r="R6" s="82"/>
+      <c r="S6" s="82"/>
+      <c r="T6" s="82"/>
+      <c r="U6" s="82"/>
+      <c r="V6" s="82"/>
+      <c r="W6" s="82"/>
     </row>
     <row r="7" ht="45" customHeight="1" spans="1:23">
-      <c r="A7" s="56" t="s">
+      <c r="A7" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="44" t="s">
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="51" t="s">
+      <c r="F7" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="50"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="44" t="s">
+      <c r="G7" s="54"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="84"/>
-      <c r="K7" s="49" t="s">
+      <c r="J7" s="88"/>
+      <c r="K7" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="L7" s="49"/>
-      <c r="N7" s="37">
+      <c r="L7" s="53"/>
+      <c r="N7" s="41">
         <v>5</v>
       </c>
-      <c r="O7" s="77" t="s">
+      <c r="O7" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="P7" s="78" t="s">
+      <c r="P7" s="82" t="s">
         <v>107</v>
       </c>
-      <c r="Q7" s="78"/>
-      <c r="R7" s="78"/>
-      <c r="S7" s="78"/>
-      <c r="T7" s="78"/>
-      <c r="U7" s="78"/>
-      <c r="V7" s="78"/>
-      <c r="W7" s="78"/>
+      <c r="Q7" s="82"/>
+      <c r="R7" s="82"/>
+      <c r="S7" s="82"/>
+      <c r="T7" s="82"/>
+      <c r="U7" s="82"/>
+      <c r="V7" s="82"/>
+      <c r="W7" s="82"/>
     </row>
     <row r="8" ht="45" customHeight="1" spans="1:23">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="44" t="s">
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="51" t="s">
+      <c r="F8" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="50"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="44" t="s">
+      <c r="G8" s="54"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="48" t="s">
         <v>108</v>
       </c>
-      <c r="J8" s="84"/>
-      <c r="K8" s="49" t="s">
+      <c r="J8" s="88"/>
+      <c r="K8" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="L8" s="49"/>
-      <c r="N8" s="37">
+      <c r="L8" s="53"/>
+      <c r="N8" s="41">
         <v>6</v>
       </c>
-      <c r="O8" s="77" t="s">
+      <c r="O8" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="P8" s="78" t="s">
+      <c r="P8" s="82" t="s">
         <v>109</v>
       </c>
-      <c r="Q8" s="78"/>
-      <c r="R8" s="78"/>
-      <c r="S8" s="78"/>
-      <c r="T8" s="78"/>
-      <c r="U8" s="78"/>
-      <c r="V8" s="94"/>
-      <c r="W8" s="94"/>
+      <c r="Q8" s="82"/>
+      <c r="R8" s="82"/>
+      <c r="S8" s="82"/>
+      <c r="T8" s="82"/>
+      <c r="U8" s="82"/>
+      <c r="V8" s="98"/>
+      <c r="W8" s="98"/>
     </row>
     <row r="9" ht="45" customHeight="1" spans="1:23">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58" t="s">
+      <c r="B9" s="62"/>
+      <c r="C9" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="58"/>
-      <c r="E9" s="59" t="s">
+      <c r="D9" s="62"/>
+      <c r="E9" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59" t="s">
+      <c r="F9" s="63"/>
+      <c r="G9" s="63" t="s">
         <v>110</v>
       </c>
-      <c r="H9" s="60"/>
-      <c r="I9" s="85" t="s">
+      <c r="H9" s="64"/>
+      <c r="I9" s="89" t="s">
         <v>111</v>
       </c>
-      <c r="J9" s="58"/>
-      <c r="K9" s="86" t="s">
+      <c r="J9" s="62"/>
+      <c r="K9" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="L9" s="59"/>
-      <c r="N9" s="37">
+      <c r="L9" s="63"/>
+      <c r="N9" s="41">
         <v>7</v>
       </c>
-      <c r="O9" s="77" t="s">
+      <c r="O9" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="P9" s="78" t="s">
+      <c r="P9" s="82" t="s">
         <v>112</v>
       </c>
-      <c r="Q9" s="78"/>
-      <c r="R9" s="78"/>
-      <c r="S9" s="78"/>
-      <c r="T9" s="78"/>
-      <c r="U9" s="78"/>
-      <c r="V9" s="94"/>
-      <c r="W9" s="78"/>
+      <c r="Q9" s="82"/>
+      <c r="R9" s="82"/>
+      <c r="S9" s="82"/>
+      <c r="T9" s="82"/>
+      <c r="U9" s="82"/>
+      <c r="V9" s="98"/>
+      <c r="W9" s="82"/>
     </row>
     <row r="10" ht="45" customHeight="1" spans="1:23">
-      <c r="A10" s="61"/>
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="62" t="s">
+      <c r="A10" s="65"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="N10" s="37">
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="65"/>
+      <c r="L10" s="65"/>
+      <c r="N10" s="41">
         <v>8</v>
       </c>
-      <c r="O10" s="77" t="s">
+      <c r="O10" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="P10" s="78" t="s">
+      <c r="P10" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="Q10" s="78"/>
-      <c r="R10" s="78"/>
-      <c r="S10" s="78"/>
-      <c r="T10" s="78"/>
-      <c r="U10" s="78"/>
-      <c r="V10" s="94"/>
-      <c r="W10" s="94"/>
+      <c r="Q10" s="82"/>
+      <c r="R10" s="82"/>
+      <c r="S10" s="82"/>
+      <c r="T10" s="82"/>
+      <c r="U10" s="82"/>
+      <c r="V10" s="98"/>
+      <c r="W10" s="98"/>
     </row>
     <row r="11" ht="45" customHeight="1" spans="1:23">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="N11" s="37">
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="43"/>
+      <c r="N11" s="41">
         <v>9</v>
       </c>
-      <c r="O11" s="77" t="s">
+      <c r="O11" s="81" t="s">
         <v>78</v>
       </c>
-      <c r="P11" s="78" t="s">
+      <c r="P11" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="Q11" s="78"/>
-      <c r="R11" s="78"/>
-      <c r="S11" s="78"/>
-      <c r="T11" s="78"/>
-      <c r="U11" s="78"/>
-      <c r="V11" s="94"/>
-      <c r="W11" s="94"/>
+      <c r="Q11" s="82"/>
+      <c r="R11" s="82"/>
+      <c r="S11" s="82"/>
+      <c r="T11" s="82"/>
+      <c r="U11" s="82"/>
+      <c r="V11" s="98"/>
+      <c r="W11" s="98"/>
     </row>
     <row r="12" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A12" s="63" t="s">
+      <c r="A12" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="63" t="s">
+      <c r="C12" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="64" t="s">
+      <c r="D12" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="64"/>
-      <c r="F12" s="65" t="s">
+      <c r="E12" s="68"/>
+      <c r="F12" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
-      <c r="I12" s="65"/>
-      <c r="J12" s="28" t="s">
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="K12" s="28"/>
-      <c r="L12" s="74" t="s">
+      <c r="K12" s="32"/>
+      <c r="L12" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="N12" s="37">
+      <c r="N12" s="41">
         <v>11</v>
       </c>
-      <c r="O12" s="77" t="s">
+      <c r="O12" s="81" t="s">
         <v>115</v>
       </c>
-      <c r="P12" s="78" t="s">
+      <c r="P12" s="82" t="s">
         <v>116</v>
       </c>
-      <c r="Q12" s="78"/>
-      <c r="R12" s="78"/>
-      <c r="S12" s="78"/>
-      <c r="T12" s="78"/>
-      <c r="U12" s="78"/>
-      <c r="V12" s="78"/>
-      <c r="W12" s="94"/>
+      <c r="Q12" s="82"/>
+      <c r="R12" s="82"/>
+      <c r="S12" s="82"/>
+      <c r="T12" s="82"/>
+      <c r="U12" s="82"/>
+      <c r="V12" s="82"/>
+      <c r="W12" s="98"/>
     </row>
     <row r="13" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="48" t="s">
+      <c r="B13" s="48"/>
+      <c r="C13" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="66"/>
-      <c r="E13" s="48" t="s">
+      <c r="D13" s="70"/>
+      <c r="E13" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="87"/>
-      <c r="J13" s="88" t="s">
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="92" t="s">
         <v>118</v>
       </c>
-      <c r="K13" s="89" t="s">
+      <c r="K13" s="93" t="s">
         <v>57</v>
       </c>
-      <c r="L13" s="44" t="s">
+      <c r="L13" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="N13" s="37">
+      <c r="N13" s="41">
         <v>12</v>
       </c>
-      <c r="O13" s="77" t="s">
+      <c r="O13" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="P13" s="78" t="s">
+      <c r="P13" s="82" t="s">
         <v>119</v>
       </c>
-      <c r="Q13" s="78"/>
-      <c r="R13" s="78"/>
-      <c r="S13" s="78"/>
-      <c r="T13" s="78"/>
-      <c r="U13" s="78"/>
-      <c r="V13" s="78"/>
-      <c r="W13" s="94"/>
+      <c r="Q13" s="82"/>
+      <c r="R13" s="82"/>
+      <c r="S13" s="82"/>
+      <c r="T13" s="82"/>
+      <c r="U13" s="82"/>
+      <c r="V13" s="82"/>
+      <c r="W13" s="98"/>
     </row>
     <row r="14" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A14" s="67" t="s">
+      <c r="A14" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="67"/>
-      <c r="C14" s="67" t="s">
+      <c r="B14" s="71"/>
+      <c r="C14" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="67"/>
-      <c r="E14" s="68" t="s">
+      <c r="D14" s="71"/>
+      <c r="E14" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="70"/>
-      <c r="J14" s="67" t="s">
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="K14" s="70" t="s">
+      <c r="K14" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="L14" s="67" t="s">
+      <c r="L14" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="N14" s="37">
+      <c r="N14" s="41">
         <v>13</v>
       </c>
-      <c r="O14" s="77" t="s">
+      <c r="O14" s="81" t="s">
         <v>120</v>
       </c>
-      <c r="P14" s="78" t="s">
+      <c r="P14" s="82" t="s">
         <v>121</v>
       </c>
-      <c r="Q14" s="78"/>
-      <c r="R14" s="78"/>
-      <c r="S14" s="78"/>
-      <c r="T14" s="78"/>
-      <c r="U14" s="78"/>
-      <c r="V14" s="78"/>
-      <c r="W14" s="94"/>
+      <c r="Q14" s="82"/>
+      <c r="R14" s="82"/>
+      <c r="S14" s="82"/>
+      <c r="T14" s="82"/>
+      <c r="U14" s="82"/>
+      <c r="V14" s="82"/>
+      <c r="W14" s="98"/>
     </row>
     <row r="15" ht="35.1" customHeight="1" spans="1:12">
-      <c r="A15" s="52" t="s">
+      <c r="A15" s="56" t="s">
         <v>122</v>
       </c>
-      <c r="B15" s="70" t="s">
+      <c r="B15" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="71" t="s">
+      <c r="C15" s="75" t="s">
         <v>123</v>
       </c>
-      <c r="D15" s="72"/>
-      <c r="E15" s="54" t="s">
+      <c r="D15" s="76"/>
+      <c r="E15" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="90" t="s">
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="94" t="s">
         <v>33</v>
       </c>
-      <c r="K15" s="91"/>
-      <c r="L15" s="92" t="s">
+      <c r="K15" s="95"/>
+      <c r="L15" s="96" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="16" ht="51.95" customHeight="1" spans="1:12">
-      <c r="A16" s="58" t="s">
+      <c r="A16" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58" t="s">
+      <c r="B16" s="62"/>
+      <c r="C16" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="58"/>
-      <c r="E16" s="59" t="s">
+      <c r="D16" s="62"/>
+      <c r="E16" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="59"/>
-      <c r="G16" s="59" t="s">
+      <c r="F16" s="63"/>
+      <c r="G16" s="63" t="s">
         <v>110</v>
       </c>
-      <c r="H16" s="60"/>
-      <c r="I16" s="85" t="s">
+      <c r="H16" s="64"/>
+      <c r="I16" s="89" t="s">
         <v>111</v>
       </c>
-      <c r="J16" s="58"/>
-      <c r="K16" s="86" t="s">
+      <c r="J16" s="62"/>
+      <c r="K16" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="L16" s="59"/>
+      <c r="L16" s="63"/>
     </row>
     <row r="17" ht="54.95" customHeight="1"/>
     <row r="18" ht="35.1" customHeight="1" spans="14:23">
-      <c r="N18" s="37">
+      <c r="N18" s="41">
         <v>1</v>
       </c>
-      <c r="O18" s="77" t="s">
+      <c r="O18" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="P18" s="78" t="s">
+      <c r="P18" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="Q18" s="78"/>
-      <c r="R18" s="78"/>
-      <c r="S18" s="78"/>
-      <c r="T18" s="78"/>
-      <c r="U18" s="78"/>
-      <c r="V18" s="78"/>
-      <c r="W18" s="78"/>
+      <c r="Q18" s="82"/>
+      <c r="R18" s="82"/>
+      <c r="S18" s="82"/>
+      <c r="T18" s="82"/>
+      <c r="U18" s="82"/>
+      <c r="V18" s="82"/>
+      <c r="W18" s="82"/>
     </row>
     <row r="19" ht="45" customHeight="1" spans="14:23">
-      <c r="N19" s="37">
+      <c r="N19" s="41">
         <v>2</v>
       </c>
-      <c r="O19" s="77" t="s">
+      <c r="O19" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="P19" s="78" t="s">
+      <c r="P19" s="82" t="s">
         <v>88</v>
       </c>
-      <c r="Q19" s="78"/>
-      <c r="R19" s="78"/>
-      <c r="S19" s="78"/>
-      <c r="T19" s="78"/>
-      <c r="U19" s="78"/>
-      <c r="V19" s="78"/>
-      <c r="W19" s="78"/>
+      <c r="Q19" s="82"/>
+      <c r="R19" s="82"/>
+      <c r="S19" s="82"/>
+      <c r="T19" s="82"/>
+      <c r="U19" s="82"/>
+      <c r="V19" s="82"/>
+      <c r="W19" s="82"/>
     </row>
     <row r="20" ht="45" customHeight="1" spans="14:23">
-      <c r="N20" s="37">
+      <c r="N20" s="41">
         <v>3</v>
       </c>
-      <c r="O20" s="77" t="s">
+      <c r="O20" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="P20" s="78" t="s">
+      <c r="P20" s="82" t="s">
         <v>105</v>
       </c>
-      <c r="Q20" s="78"/>
-      <c r="R20" s="78"/>
-      <c r="S20" s="78"/>
-      <c r="T20" s="78"/>
-      <c r="U20" s="78"/>
-      <c r="V20" s="78"/>
-      <c r="W20" s="78"/>
+      <c r="Q20" s="82"/>
+      <c r="R20" s="82"/>
+      <c r="S20" s="82"/>
+      <c r="T20" s="82"/>
+      <c r="U20" s="82"/>
+      <c r="V20" s="82"/>
+      <c r="W20" s="82"/>
     </row>
     <row r="21" ht="45" customHeight="1" spans="14:23">
-      <c r="N21" s="37">
+      <c r="N21" s="41">
         <v>4</v>
       </c>
-      <c r="O21" s="77" t="s">
+      <c r="O21" s="81" t="s">
         <v>55</v>
       </c>
-      <c r="P21" s="78" t="s">
+      <c r="P21" s="82" t="s">
         <v>124</v>
       </c>
-      <c r="Q21" s="78"/>
-      <c r="R21" s="78"/>
-      <c r="S21" s="78"/>
-      <c r="T21" s="78"/>
-      <c r="U21" s="78"/>
-      <c r="V21" s="78"/>
-      <c r="W21" s="94"/>
+      <c r="Q21" s="82"/>
+      <c r="R21" s="82"/>
+      <c r="S21" s="82"/>
+      <c r="T21" s="82"/>
+      <c r="U21" s="82"/>
+      <c r="V21" s="82"/>
+      <c r="W21" s="98"/>
     </row>
     <row r="22" ht="45" customHeight="1" spans="14:23">
-      <c r="N22" s="37">
+      <c r="N22" s="41">
         <v>5</v>
       </c>
-      <c r="O22" s="77" t="s">
+      <c r="O22" s="81" t="s">
         <v>23</v>
       </c>
-      <c r="P22" s="78" t="s">
+      <c r="P22" s="82" t="s">
         <v>125</v>
       </c>
-      <c r="Q22" s="78"/>
-      <c r="R22" s="78"/>
-      <c r="S22" s="78"/>
-      <c r="T22" s="78"/>
-      <c r="U22" s="78"/>
-      <c r="V22" s="78"/>
-      <c r="W22" s="78"/>
+      <c r="Q22" s="82"/>
+      <c r="R22" s="82"/>
+      <c r="S22" s="82"/>
+      <c r="T22" s="82"/>
+      <c r="U22" s="82"/>
+      <c r="V22" s="82"/>
+      <c r="W22" s="82"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="14:23">
-      <c r="N23" s="37">
+      <c r="N23" s="41">
         <v>6</v>
       </c>
-      <c r="O23" s="77" t="s">
+      <c r="O23" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="P23" s="78" t="s">
+      <c r="P23" s="82" t="s">
         <v>126</v>
       </c>
-      <c r="Q23" s="78"/>
-      <c r="R23" s="78"/>
-      <c r="S23" s="78"/>
-      <c r="T23" s="78"/>
-      <c r="U23" s="78"/>
-      <c r="V23" s="94"/>
-      <c r="W23" s="94"/>
+      <c r="Q23" s="82"/>
+      <c r="R23" s="82"/>
+      <c r="S23" s="82"/>
+      <c r="T23" s="82"/>
+      <c r="U23" s="82"/>
+      <c r="V23" s="98"/>
+      <c r="W23" s="98"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="14:23">
-      <c r="N24" s="37">
+      <c r="N24" s="41">
         <v>7</v>
       </c>
-      <c r="O24" s="77" t="s">
+      <c r="O24" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="P24" s="78" t="s">
+      <c r="P24" s="82" t="s">
         <v>119</v>
       </c>
-      <c r="Q24" s="78"/>
-      <c r="R24" s="78"/>
-      <c r="S24" s="78"/>
-      <c r="T24" s="78"/>
-      <c r="U24" s="78"/>
-      <c r="V24" s="78"/>
-      <c r="W24" s="78"/>
+      <c r="Q24" s="82"/>
+      <c r="R24" s="82"/>
+      <c r="S24" s="82"/>
+      <c r="T24" s="82"/>
+      <c r="U24" s="82"/>
+      <c r="V24" s="82"/>
+      <c r="W24" s="82"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="14:23">
-      <c r="N25" s="37">
+      <c r="N25" s="41">
         <v>8</v>
       </c>
-      <c r="O25" s="77" t="s">
+      <c r="O25" s="81" t="s">
         <v>120</v>
       </c>
-      <c r="P25" s="78" t="s">
+      <c r="P25" s="82" t="s">
         <v>121</v>
       </c>
-      <c r="Q25" s="78"/>
-      <c r="R25" s="78"/>
-      <c r="S25" s="78"/>
-      <c r="T25" s="78"/>
-      <c r="U25" s="78"/>
-      <c r="V25" s="78"/>
-      <c r="W25" s="94"/>
+      <c r="Q25" s="82"/>
+      <c r="R25" s="82"/>
+      <c r="S25" s="82"/>
+      <c r="T25" s="82"/>
+      <c r="U25" s="82"/>
+      <c r="V25" s="82"/>
+      <c r="W25" s="98"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="14:21">
-      <c r="N26" s="37"/>
-      <c r="O26" s="77"/>
-      <c r="P26" s="93"/>
-      <c r="Q26" s="93"/>
-      <c r="R26" s="93"/>
-      <c r="S26" s="93"/>
-      <c r="T26" s="93"/>
-      <c r="U26" s="93"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="81"/>
+      <c r="P26" s="97"/>
+      <c r="Q26" s="97"/>
+      <c r="R26" s="97"/>
+      <c r="S26" s="97"/>
+      <c r="T26" s="97"/>
+      <c r="U26" s="97"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="14:23">
-      <c r="N27" s="37"/>
-      <c r="O27" s="77"/>
-      <c r="P27" s="93"/>
-      <c r="Q27" s="93"/>
-      <c r="R27" s="93"/>
-      <c r="S27" s="93"/>
-      <c r="T27" s="93"/>
-      <c r="U27" s="93"/>
-      <c r="V27" s="93"/>
-      <c r="W27" s="93"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="81"/>
+      <c r="P27" s="97"/>
+      <c r="Q27" s="97"/>
+      <c r="R27" s="97"/>
+      <c r="S27" s="97"/>
+      <c r="T27" s="97"/>
+      <c r="U27" s="97"/>
+      <c r="V27" s="97"/>
+      <c r="W27" s="97"/>
     </row>
     <row r="28" ht="35.1" customHeight="1" spans="14:22">
-      <c r="N28" s="37"/>
-      <c r="O28" s="77"/>
-      <c r="P28" s="93"/>
-      <c r="Q28" s="93"/>
-      <c r="R28" s="93"/>
-      <c r="S28" s="93"/>
-      <c r="T28" s="93"/>
-      <c r="U28" s="93"/>
-      <c r="V28" s="93"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="81"/>
+      <c r="P28" s="97"/>
+      <c r="Q28" s="97"/>
+      <c r="R28" s="97"/>
+      <c r="S28" s="97"/>
+      <c r="T28" s="97"/>
+      <c r="U28" s="97"/>
+      <c r="V28" s="97"/>
     </row>
     <row r="29" ht="35.1" customHeight="1"/>
   </sheetData>
@@ -4530,124 +6018,124 @@
   </cols>
   <sheetData>
     <row r="1" ht="75" customHeight="1" spans="1:8">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" ht="36" customHeight="1" spans="1:8">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="27"/>
-      <c r="G2" s="28" t="s">
+      <c r="F2" s="31"/>
+      <c r="G2" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="33" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" ht="65.1" customHeight="1" spans="1:8">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34" t="s">
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="H3" s="33"/>
+      <c r="H3" s="37"/>
     </row>
     <row r="4" ht="65.1" customHeight="1" spans="1:8">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="33"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="37"/>
     </row>
     <row r="5" ht="65.1" customHeight="1" spans="1:8">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="31" t="s">
+      <c r="B5" s="38"/>
+      <c r="C5" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="D5" s="32"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="34" t="s">
+      <c r="D5" s="36"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="H5" s="33"/>
+      <c r="H5" s="37"/>
     </row>
     <row r="6" ht="65.1" customHeight="1" spans="1:8">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="31" t="s">
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="33"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="37"/>
     </row>
     <row r="7" ht="65.1" customHeight="1" spans="1:8">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37" t="s">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="D7" s="37"/>
-      <c r="E7" s="38" t="s">
+      <c r="D7" s="41"/>
+      <c r="E7" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="H7" s="38"/>
+      <c r="H7" s="42"/>
     </row>
     <row r="8" ht="42.95" customHeight="1"/>
     <row r="9" ht="42.95" customHeight="1"/>
@@ -4688,1368 +6176,254 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet7">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:T53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="1"/>
   <cols>
-    <col min="4" max="4" width="5.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="4.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="4.875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="14" style="1" customWidth="1"/>
+    <col min="1" max="1" width="32.375" customWidth="1"/>
+    <col min="2" max="2" width="4.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.375" customWidth="1"/>
+    <col min="8" max="8" width="14" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" customHeight="1" spans="1:20">
-      <c r="A1" s="18" t="s">
+    <row r="1" ht="396" customHeight="1" spans="1:14">
+      <c r="A1" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="18" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="K1" s="14" t="s">
-        <v>143</v>
-      </c>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
       <c r="L1" s="14"/>
       <c r="M1" s="14"/>
       <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-    </row>
-    <row r="2" customHeight="1" spans="1:20">
-      <c r="A2" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="15"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-    </row>
-    <row r="3" customHeight="1" spans="1:20">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="16"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:20">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="16"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
-    </row>
-    <row r="5" ht="14.25" customHeight="1" spans="1:20">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="16"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14"/>
-      <c r="T5" s="14"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:9">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="16"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:9">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="16"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:9">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="16"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:12">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="16"/>
-      <c r="L9" s="21"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:9">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="16"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:9">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="16"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:9">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="16"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:9">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="16"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:9">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="16"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:9">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="16"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:9">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="16"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:9">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="16"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:9">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="16"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:9">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="16"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:9">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="16"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:9">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="16"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:9">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="16"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:9">
-      <c r="A23" s="5"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="16"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:9">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="16"/>
-    </row>
-    <row r="25" ht="59.1" customHeight="1" spans="1:9">
-      <c r="A25" s="7"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="17"/>
-    </row>
-    <row r="26" ht="36" customHeight="1" spans="1:9">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-    </row>
-    <row r="27" ht="30.95" customHeight="1" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-    </row>
-    <row r="28" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A28" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:9">
-      <c r="A29" s="3"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="15"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:9">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="16"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:9">
-      <c r="A31" s="5"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="16"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:9">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="16"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:9">
-      <c r="A33" s="5"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="16"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:9">
-      <c r="A34" s="5"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="16"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:9">
-      <c r="A35" s="5"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="16"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:9">
-      <c r="A36" s="5"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="16"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:9">
-      <c r="A37" s="5"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="16"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:9">
-      <c r="A38" s="5"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="16"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:9">
-      <c r="A39" s="5"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="16"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:9">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="16"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:9">
-      <c r="A41" s="5"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="16"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:9">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="16"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:9">
-      <c r="A43" s="5"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="16"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:9">
-      <c r="A44" s="5"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="16"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:9">
-      <c r="A45" s="5"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="16"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:9">
-      <c r="A46" s="5"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="16"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:9">
-      <c r="A47" s="5"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="16"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:9">
-      <c r="A48" s="5"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="16"/>
-    </row>
-    <row r="49" customHeight="1" spans="1:9">
-      <c r="A49" s="5"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="16"/>
-    </row>
-    <row r="50" customHeight="1" spans="1:9">
-      <c r="A50" s="5"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="16"/>
-    </row>
-    <row r="51" customHeight="1" spans="1:9">
-      <c r="A51" s="5"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="16"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:9">
-      <c r="A52" s="5"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="16"/>
-    </row>
-    <row r="53" ht="42" customHeight="1" spans="1:9">
-      <c r="A53" s="7"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="20"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="17"/>
+    </row>
+    <row r="2" ht="13" customHeight="1" spans="1:3">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
     </row>
   </sheetData>
-  <protectedRanges>
-    <protectedRange password="C6E5" sqref="F29" name="区域4"/>
-    <protectedRange password="C6E5" sqref="A2" name="区域1"/>
-    <protectedRange password="C6E5" sqref="F2" name="区域2"/>
-    <protectedRange password="C6E5" sqref="A29" name="区域3"/>
-  </protectedRanges>
-  <mergeCells count="12">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="K5:P5"/>
-    <mergeCell ref="Q5:T5"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="F29:I53"/>
-    <mergeCell ref="F2:I25"/>
-    <mergeCell ref="A29:D53"/>
-    <mergeCell ref="Q1:T4"/>
-    <mergeCell ref="K1:P4"/>
-    <mergeCell ref="A2:D25"/>
+  <mergeCells count="2">
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="K1:N1"/>
   </mergeCells>
   <pageMargins left="1.02361111111111" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet8">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:U53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="1"/>
   <cols>
-    <col min="4" max="4" width="11.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="8" max="8" width="4.25" customWidth="1"/>
-    <col min="9" max="9" width="7.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="76.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" customHeight="1" spans="1:21">
-      <c r="A1" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="L1" s="14" t="s">
-        <v>143</v>
-      </c>
+    <row r="1" ht="369" customHeight="1" spans="1:13">
+      <c r="A1" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
       <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-    </row>
-    <row r="2" customHeight="1" spans="1:21">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="15"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-    </row>
-    <row r="3" customHeight="1" spans="1:21">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="16"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:21">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="16"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
-    </row>
-    <row r="5" ht="14.25" customHeight="1" spans="1:21">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="16"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="14"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:9">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="16"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:9">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="16"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:9">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="16"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:9">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="16"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:9">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="16"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:9">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="16"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:9">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="16"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:9">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="16"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:9">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="16"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:9">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="16"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:9">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="16"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:9">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="16"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:9">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="16"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:9">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="16"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:9">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="16"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:9">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="16"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:9">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="16"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:9">
-      <c r="A23" s="5"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="16"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:9">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="16"/>
-    </row>
-    <row r="25" ht="17.1" customHeight="1" spans="1:9">
-      <c r="A25" s="7"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="17"/>
-    </row>
-    <row r="26" ht="36" customHeight="1" spans="1:9">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-    </row>
-    <row r="27" ht="30.95" customHeight="1" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-    </row>
-    <row r="28" ht="20.1" customHeight="1" spans="1:9">
-      <c r="A28" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:9">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:9">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:9">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:9">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:9">
-      <c r="A33" s="13"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:9">
-      <c r="A34" s="13"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:9">
-      <c r="A35" s="13"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:9">
-      <c r="A36" s="13"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:9">
-      <c r="A37" s="13"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:9">
-      <c r="A38" s="13"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:9">
-      <c r="A39" s="13"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:9">
-      <c r="A40" s="13"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:9">
-      <c r="A41" s="13"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:9">
-      <c r="A42" s="13"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:9">
-      <c r="A43" s="13"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:9">
-      <c r="A44" s="13"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:9">
-      <c r="A45" s="13"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:9">
-      <c r="A46" s="13"/>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:9">
-      <c r="A47" s="13"/>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="13"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:9">
-      <c r="A48" s="13"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-    </row>
-    <row r="49" customHeight="1" spans="1:9">
-      <c r="A49" s="13"/>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-    </row>
-    <row r="50" customHeight="1" spans="1:9">
-      <c r="A50" s="13"/>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-    </row>
-    <row r="51" customHeight="1" spans="1:9">
-      <c r="A51" s="13"/>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:9">
-      <c r="A52" s="13"/>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-    </row>
-    <row r="53" customHeight="1" spans="1:9">
-      <c r="A53" s="13"/>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="13"/>
+    </row>
+    <row r="2" ht="12" customHeight="1" spans="1:1">
+      <c r="A2" s="9"/>
     </row>
   </sheetData>
-  <protectedRanges>
-    <protectedRange sqref="F2" name="区域2"/>
-    <protectedRange sqref="A2" name="区域1"/>
-    <protectedRange sqref="F29" name="区域4"/>
-    <protectedRange sqref="A29" name="区域3"/>
-  </protectedRanges>
-  <mergeCells count="8">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="L5:Q5"/>
-    <mergeCell ref="R5:U5"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A29:I53"/>
-    <mergeCell ref="A2:I25"/>
-    <mergeCell ref="L1:Q4"/>
-    <mergeCell ref="R1:U4"/>
+  <mergeCells count="2">
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="J1:M1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="5"/>
+  <cols>
+    <col min="1" max="1" width="32.375" customWidth="1"/>
+    <col min="2" max="2" width="4.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.375" customWidth="1"/>
+    <col min="8" max="8" width="14" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A1" s="24"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="18"/>
+    </row>
+    <row r="2" ht="368" customHeight="1" spans="1:14">
+      <c r="A2" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="1:3">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+    </row>
+    <row r="4" ht="30.95" customHeight="1" spans="1:3">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A5" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" ht="368" customHeight="1" spans="1:3">
+      <c r="A6" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange sqref="C6" name="区域4"/>
+    <protectedRange sqref="A2" name="区域1"/>
+    <protectedRange sqref="C2" name="区域2"/>
+    <protectedRange sqref="A6" name="区域3"/>
+  </protectedRanges>
+  <mergeCells count="2">
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="K2:N2"/>
+  </mergeCells>
+  <pageMargins left="1.02361111111111" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet7">
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="32.375" customWidth="1"/>
+    <col min="2" max="2" width="4.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.375" customWidth="1"/>
+    <col min="8" max="8" width="14" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="385" customHeight="1" spans="1:14">
+      <c r="A1" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="1.02361111111111" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet8">
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="76.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="357" customHeight="1" spans="1:13">
+      <c r="A1" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="J1:M1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6061,13 +6435,27 @@
   <rangeList sheetStid="3" master="">
     <arrUserId title="区域1" rangeCreator="" othersAccessPermission="edit"/>
   </rangeList>
-  <rangeList sheetStid="7" master="">
+  <rangeList sheetStid="13" master="">
+    <arrUserId title="区域1" rangeCreator="" othersAccessPermission="edit"/>
+    <arrUserId title="区域2" rangeCreator="" othersAccessPermission="edit"/>
+  </rangeList>
+  <rangeList sheetStid="16" master=""/>
+  <rangeList sheetStid="15" master="">
     <arrUserId title="区域4" rangeCreator="" othersAccessPermission="edit"/>
     <arrUserId title="区域1" rangeCreator="" othersAccessPermission="edit"/>
     <arrUserId title="区域2" rangeCreator="" othersAccessPermission="edit"/>
     <arrUserId title="区域3" rangeCreator="" othersAccessPermission="edit"/>
   </rangeList>
-  <rangeList sheetStid="8" master="">
+  <rangeList sheetStid="7" master=""/>
+  <rangeList sheetStid="8" master=""/>
+  <rangeList sheetStid="14" master=""/>
+  <rangeList sheetStid="11" master="">
+    <arrUserId title="区域4" rangeCreator="" othersAccessPermission="edit"/>
+    <arrUserId title="区域1" rangeCreator="" othersAccessPermission="edit"/>
+    <arrUserId title="区域2" rangeCreator="" othersAccessPermission="edit"/>
+    <arrUserId title="区域3" rangeCreator="" othersAccessPermission="edit"/>
+  </rangeList>
+  <rangeList sheetStid="12" master="">
     <arrUserId title="区域2" rangeCreator="" othersAccessPermission="edit"/>
     <arrUserId title="区域1" rangeCreator="" othersAccessPermission="edit"/>
     <arrUserId title="区域4" rangeCreator="" othersAccessPermission="edit"/>
